--- a/data/trans_bre/IP17-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 6,22</t>
+          <t>-7,96; 6,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 10,69</t>
+          <t>-6,46; 9,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 5,03</t>
+          <t>-10,49; 5,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 7,31</t>
+          <t>-8,73; 7,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-36,43; 36,46</t>
+          <t>-33,57; 40,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 63,1</t>
+          <t>-25,65; 58,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,25; 31,21</t>
+          <t>-43,17; 32,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 65,17</t>
+          <t>-44,71; 69,08</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 7,22</t>
+          <t>-6,13; 6,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 5,73</t>
+          <t>-7,62; 6,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 10,16</t>
+          <t>-3,32; 9,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 1,58</t>
+          <t>-11,04; 1,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 37,9</t>
+          <t>-24,25; 36,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 29,12</t>
+          <t>-28,12; 31,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 54,8</t>
+          <t>-13,44; 52,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 10,02</t>
+          <t>-48,1; 9,39</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 2,09</t>
+          <t>-12,9; 1,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 3,86</t>
+          <t>-12,07; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 7,82</t>
+          <t>-5,99; 7,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 3,76</t>
+          <t>-10,81; 5,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-47,79; 12,33</t>
+          <t>-49,07; 9,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 18,62</t>
+          <t>-41,27; 9,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 50,93</t>
+          <t>-27,6; 55,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-56,03; 26,17</t>
+          <t>-54,33; 42,95</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 0,94</t>
+          <t>-12,12; 0,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 10,8</t>
+          <t>-2,89; 10,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 5,89</t>
+          <t>-6,99; 6,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 7,65</t>
+          <t>-6,02; 7,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,41; 4,95</t>
+          <t>-44,34; 2,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 62,39</t>
+          <t>-12,56; 62,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,24; 37,62</t>
+          <t>-32,45; 40,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 63,15</t>
+          <t>-30,67; 55,97</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,3</t>
+          <t>-6,5; 0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,81</t>
+          <t>-3,56; 3,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 4,43</t>
+          <t>-2,71; 4,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,19</t>
+          <t>-6,11; 1,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 1,41</t>
+          <t>-26,78; 2,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 18,17</t>
+          <t>-14,3; 18,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 25,54</t>
+          <t>-12,32; 22,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 8,15</t>
+          <t>-31,29; 10,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,85</t>
+          <t>-9,0; 7,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 9,87</t>
+          <t>-5,58; 10,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 5,17</t>
+          <t>-10,98; 4,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 7,73</t>
+          <t>-9,21; 7,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 40,55</t>
+          <t>-35,92; 45,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 58,49</t>
+          <t>-22,71; 64,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 32,47</t>
+          <t>-43,74; 27,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,71; 69,08</t>
+          <t>-46,53; 64,24</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 6,77</t>
+          <t>-5,95; 6,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 6,25</t>
+          <t>-7,61; 5,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 9,87</t>
+          <t>-2,25; 10,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 1,69</t>
+          <t>-9,81; 2,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 36,08</t>
+          <t>-23,88; 33,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 31,12</t>
+          <t>-28,65; 28,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 52,2</t>
+          <t>-9,67; 54,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 9,39</t>
+          <t>-44,89; 19,94</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 1,67</t>
+          <t>-13,02; 1,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 2,27</t>
+          <t>-12,05; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 7,89</t>
+          <t>-5,17; 8,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 5,77</t>
+          <t>-11,07; 5,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 9,22</t>
+          <t>-48,76; 8,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,27; 9,36</t>
+          <t>-39,67; 15,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 55,73</t>
+          <t>-24,43; 58,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-54,33; 42,95</t>
+          <t>-55,28; 36,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 0,53</t>
+          <t>-11,9; 0,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 10,91</t>
+          <t>-3,25; 10,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 6,26</t>
+          <t>-6,5; 6,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 7,06</t>
+          <t>-5,67; 7,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 2,87</t>
+          <t>-44,09; 5,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 62,58</t>
+          <t>-12,64; 62,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 40,82</t>
+          <t>-31,09; 45,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 55,97</t>
+          <t>-29,85; 55,09</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,45</t>
+          <t>-6,11; 0,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,89</t>
+          <t>-3,24; 4,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,1</t>
+          <t>-2,62; 4,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 1,53</t>
+          <t>-5,76; 1,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 2,8</t>
+          <t>-25,52; 4,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 18,47</t>
+          <t>-13,53; 22,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 22,8</t>
+          <t>-12,8; 22,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 10,46</t>
+          <t>-30,44; 7,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han necesitado consulta del médico en las últimas 2 semanas</t>
+          <t>Menores que han necesitado consulta médica en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,89</t>
+          <t>-1,76</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,76%</t>
+          <t>-11,05%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 7,48</t>
+          <t>-8,97; 6,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 10,73</t>
+          <t>-6,28; 10,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 4,77</t>
+          <t>-10,34; 5,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 7,12</t>
+          <t>-8,95; 6,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,92; 45,39</t>
+          <t>-36,43; 36,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 64,52</t>
+          <t>-24,15; 63,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 27,32</t>
+          <t>-43,25; 31,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,53; 64,24</t>
+          <t>-46,66; 56,87</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,29</t>
+          <t>-4,52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-22,01%</t>
+          <t>-23,64%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 6,68</t>
+          <t>-5,83; 7,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 5,86</t>
+          <t>-7,1; 5,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,07</t>
+          <t>-3,03; 10,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 2,93</t>
+          <t>-10,33; 1,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 33,53</t>
+          <t>-22,98; 37,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 28,46</t>
+          <t>-27,02; 29,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 54,69</t>
+          <t>-12,41; 54,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 19,94</t>
+          <t>-47,82; 7,95</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,26</t>
+          <t>-2,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-19,06%</t>
+          <t>-15,31%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 1,43</t>
+          <t>-12,25; 2,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 3,12</t>
+          <t>-11,07; 3,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 8,14</t>
+          <t>-5,31; 7,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 5,04</t>
+          <t>-11,09; 3,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 8,61</t>
+          <t>-47,79; 12,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-39,67; 15,43</t>
+          <t>-38,75; 18,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 58,05</t>
+          <t>-24,61; 50,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-55,28; 36,79</t>
+          <t>-48,63; 28,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 0,96</t>
+          <t>-11,73; 0,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 10,77</t>
+          <t>-3,01; 10,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 6,63</t>
+          <t>-6,4; 5,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 7,06</t>
+          <t>-5,45; 7,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 5,25</t>
+          <t>-45,41; 4,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 62,5</t>
+          <t>-12,89; 62,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,09; 45,26</t>
+          <t>-30,24; 37,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,85; 55,09</t>
+          <t>-29,57; 58,93</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-2,18</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,7%</t>
+          <t>-12,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,94</t>
+          <t>-6,45; 0,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,44</t>
+          <t>-3,79; 3,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,06</t>
+          <t>-2,61; 4,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,16</t>
+          <t>-6,0; 0,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 4,47</t>
+          <t>-26,75; 1,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 22,1</t>
+          <t>-15,18; 18,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,8; 22,07</t>
+          <t>-12,18; 25,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 7,61</t>
+          <t>-30,64; 6,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP17-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP17-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,79</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,55%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-13,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-11,05%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.7448594755685684</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>2.086488851549337</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-2.78555762990918</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-1.758813417619898</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.03549075213552705</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.09892869103731443</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1341615922690856</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1104842240981972</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,97; 6,22</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,28; 10,69</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,34; 5,03</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-8,95; 6,6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-36,43; 36,46</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-24,15; 63,1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-43,25; 31,21</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-46,66; 56,87</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.965788047114714</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.277558199981232</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.34305168802998</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-8.949025780834253</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3642931468094269</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2415177293712059</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.4325362527643722</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.466560107408261</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.222684175446439</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.69194788770882</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.031444578979548</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.596646835879441</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3646471046704333</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.6309811181502281</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.3120629853653745</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.5686623167692043</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,86</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,52</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-3,07%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-23,64%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,83; 7,22</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,1; 5,73</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,03; 10,16</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-10,33; 1,33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-22,98; 37,9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-27,02; 29,12</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-12,41; 54,8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-47,82; 7,95</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.4297389665119083</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.722617430736941</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.863227835985217</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.523358427029703</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01909395530060573</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.03074851880199216</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.1802709224946564</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2363729207855474</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,67</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-4,57</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,24</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,75</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-24,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-17,81%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-15,31%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.828919025702616</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.098195876164128</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.033856607842949</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.32645618540888</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2298051046191619</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2701787799652089</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1241110926587916</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4781750276641983</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-12,25; 2,09</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-11,07; 3,86</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,31; 7,82</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-11,09; 3,86</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-47,79; 12,33</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-38,75; 18,62</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-24,61; 50,93</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-48,63; 28,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.219531687074859</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.733011590670705</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10.16204709655747</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.3264435298079</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.3790435389051278</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2911837609071434</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.5480268234977157</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.07953491892553538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,28</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,75</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-22,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-1,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-5.672531585170066</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-4.571825562112405</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.236137639256574</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.745776200617628</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2496609922473604</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1780796790359399</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.067317237688718</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1531422270351833</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-11,73; 0,94</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 10,8</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,4; 5,89</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 7,45</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-45,41; 4,95</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-12,89; 62,39</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-30,24; 37,62</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-29,57; 58,93</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-12.24796895014102</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.0740666707214</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.308282762283121</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-11.09269919766089</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.4778900804894748</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3874828607953263</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2460673166116051</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.4863124694999379</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.089348591737323</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.862570831775974</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.822815101774366</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.856736671499329</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1233498723431992</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1862291144770478</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5093456083730078</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2823847625957054</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-5.282611855713257</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>3.750388743608235</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.2915489784572595</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.16225883784383</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.228909403340108</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1812774525885426</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.01602129832922955</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.07541711101499804</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-11.73001510645596</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.012045599192474</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.397335641208793</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.44575183638454</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4541377855331763</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1289341425231425</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.3023941524054236</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.295702739456925</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9360892796592299</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>10.7983811857288</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.886530866799421</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.450571379163728</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.04948531410489201</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6238600897266797</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.3762243212773068</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.5892877702479502</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-2,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-12,4%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-12,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,45; 0,3</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 3,81</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 4,43</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 0,93</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,75; 1,41</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-15,18; 18,17</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-12,18; 25,54</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-30,64; 6,0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.777549745515398</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.2721518253771343</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.742484680828992</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-2.179492267035144</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1240348381646639</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.01198507573561369</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03764575658544685</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.1254872386479975</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-6.445311372306225</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.787330492014624</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.61348695625298</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.000409658346887</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.267513060741268</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1518363107115851</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1217768689652747</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.3064241057909387</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.3033190192871209</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.813732180073707</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.431683644868994</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.9327636783477417</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.01408979416886108</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1816768411742733</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.2553692873691689</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.05996079901019331</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
